--- a/results/Int Task Remove ACC 0.7/Linea_2_permute.xlsx
+++ b/results/Int Task Remove ACC 0.7/Linea_2_permute.xlsx
@@ -446,81 +446,81 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6884258383647341</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6865628864479523</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6648235978759002</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6648235978759002</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6648235978759002</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6639157634392958</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6639157634392958</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6635207681676002</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11">
@@ -530,297 +530,297 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6671906597803157</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6657787153560777</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6583509129264566</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6640576125700153</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5101607623481487</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5094267840256056</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5094267840256056</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5037819160544119</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5114606823306903</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5124776314832327</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5124776314832327</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5124776314832327</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5029599185276787</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5071397395795446</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5055037462719139</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5055037462719139</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5067476540336073</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5118884120171674</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5118884120171674</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5076554884702117</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5192340146941151</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5209289299483524</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5204779224558086</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5207608932858078</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5210555030188405</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5130232050629228</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5159060158580053</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.506941878227977</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5069978904488252</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5063199243471302</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="41">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5058456390485196</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="42">
@@ -840,93 +840,93 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5053946315559759</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4964952353240707</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4957612570015276</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4981341383574598</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.496271186440678</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.496271186440678</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4920884556630538</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5090907107005165</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5090907107005165</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -936,7 +936,7 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -946,7 +946,7 @@
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -956,7 +956,7 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -966,7 +966,7 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -976,7 +976,7 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -986,7 +986,7 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -996,7 +996,7 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1006,7 +1006,7 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1016,7 +1016,7 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1026,7 +1026,7 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1036,7 +1036,7 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1046,7 +1046,7 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1056,7 +1056,7 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1066,47 +1066,47 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5115254237288136</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5115254237288136</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5115254237288136</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5115254237288136</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1116,7 +1116,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1126,7 +1126,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1136,7 +1136,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1146,7 +1146,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1156,7 +1156,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1166,7 +1166,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1176,7 +1176,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1186,7 +1186,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1196,7 +1196,7 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -1206,7 +1206,7 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -1216,7 +1216,7 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -1226,7 +1226,7 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -1236,7 +1236,7 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -1246,7 +1246,7 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -1256,7 +1256,7 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -1266,7 +1266,7 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1276,7 +1276,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1286,7 +1286,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1296,7 +1296,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1306,7 +1306,7 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1316,7 +1316,7 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
